--- a/outputs/20261005-learning-plan/AI解决方案工程师_动态学习清单_ORM更新版.xlsx
+++ b/outputs/20261005-learning-plan/AI解决方案工程师_动态学习清单_ORM更新版.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进度总览" sheetId="1" r:id="Rcc9160d937f94f2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日清单" sheetId="2" r:id="Rbf7ae517e7c94541"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学习资料" sheetId="3" r:id="Rdf7c4ae678234a4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="进度总览" sheetId="1" r:id="Rab2ea0c0fcde40b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="每日清单" sheetId="2" r:id="R648a786a025b474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="学习资料" sheetId="3" r:id="R268c281a389b49e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3623,7 +3623,7 @@
     </x:row>
     <x:row r="3" ht="16.5">
       <x:c r="A3" s="3" t="str">
-        <x:v>当前 day16：消息内容块与多模态；历史截取延期，每晚22:30跟进。</x:v>
+        <x:v>P05 结构化输出已完成（用户确认）；当前跟进 week03/day21。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -3658,7 +3658,7 @@
       </x:c>
       <x:c r="D5" s="28" t="n">
         <x:f>COUNTIFS(每日清单!$H$6:$H$75,"已完成")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E5" s="27" t="s">
         <x:v>4</x:v>
@@ -3672,7 +3672,7 @@
       </x:c>
       <x:c r="H5" s="29" t="n">
         <x:f>D5/B5</x:f>
-        <x:v>0.02857142857142857</x:v>
+        <x:v>0.04285714285714286</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="30" customHeight="1">
@@ -3695,7 +3695,7 @@
       </x:c>
       <x:c r="F6" s="28" t="n">
         <x:f>COUNTIFS(每日清单!$H$6:$H$75,"未开始")</x:f>
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G6" s="27" t="s">
         <x:v>9</x:v>
@@ -3734,7 +3734,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B9" s="1" t="str">
-        <x:v>基础接口/调用链免验收；当前看消息结构、输出提取与自主修改；历史截取后补。</x:v>
+        <x:v>完成记录注明依据；当前看独立修改与运行效果。历史截取继续延期。</x:v>
       </x:c>
       <x:c r="C9" s="1"/>
       <x:c r="D9" s="1"/>
@@ -3792,7 +3792,7 @@
       </x:c>
       <x:c r="D12" s="33" t="n">
         <x:f>COUNTIFS(每日清单!$B$6:$B$75,$A12,每日清单!$H$6:$H$75,"已完成")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E12" s="33" t="n">
         <x:f>COUNTIFS(每日清单!$B$6:$B$75,$A12,每日清单!$H$6:$H$75,"进行中")</x:f>
@@ -3800,7 +3800,7 @@
       </x:c>
       <x:c r="F12" s="35" t="n">
         <x:f t="shared" ref="F12:F21" si="0">D12/C12</x:f>
-        <x:v>0.2857142857142857</x:v>
+        <x:v>0.42857142857142855</x:v>
       </x:c>
       <x:c r="G12" s="34" t="s">
         <x:v>18</x:v>
@@ -4365,7 +4365,7 @@
     </x:row>
     <x:row r="3" ht="16.5">
       <x:c r="A3" s="3" t="str">
-        <x:v>当前重点：day16 消息内容块与多模态；历史截取延期。每日22:30跟进，黄色格保留手填进度。</x:v>
+        <x:v>P05 结构化输出已完成；沿 week03/day21 中间件继续。黄色手填进度保留。</x:v>
       </x:c>
       <x:c r="B3" s="4"/>
       <x:c r="C3" s="4"/>
@@ -4666,11 +4666,15 @@
       <x:c r="G10" s="8" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="H10" s="17" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="I10" s="18"/>
-      <x:c r="J10" s="19"/>
+      <x:c r="H10" s="17" t="str">
+        <x:v>已完成</x:v>
+      </x:c>
+      <x:c r="I10" s="18" t="d">
+        <x:v>2026-10-20T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J10" s="19" t="str">
+        <x:v>按用户确认记为完成；不宣称助手已独立复现全部验收。</x:v>
+      </x:c>
       <x:c r="K10" s="20">
         <x:v>46304</x:v>
       </x:c>
@@ -4683,7 +4687,9 @@
       <x:c r="N10" s="9" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="O10" s="19"/>
+      <x:c r="O10" s="19" t="str">
+        <x:v>2026-10-20用户明确要求“结构化输出标记已完成”。</x:v>
+      </x:c>
       <x:c r="P10" s="8" t="s">
         <x:v>114</x:v>
       </x:c>
@@ -7624,143 +7630,143 @@
     </x:dataValidation>
   </x:dataValidations>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="R9396a763d8bb4211"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="Raaaac5de0f834df9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="Rb54b0c1ddce045ac"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="R3f6807ddb0104775"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="Rfa4ea6d0356e471f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="R0227835c23994d45"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="R5787e49ad8794533"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="R51bf58a2a9824086"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="R75da0ae08d6a432b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="R11f8661d2efe4211"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="R4a55a09218c84d77"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="Rf5e143736f814b61"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="Rfcb57c29b6784c21"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="R09fd2797d47f4c23"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="R85d270f2b18f47ee"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="R05398e0acae543e0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="R52d8b165a5bb4a33"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="R9cc524240ef34f72"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="R39232968ce5e46c8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="Rd47d18c2b2d64aee"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="R514d9fe67c6a44c9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="R1ca95846cc374d30"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="Rdb5e0f1d344f4978"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="R514e3dd573934fd6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="R88a54668edf74756"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="Rf16a92dcf0444fd7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="R6d0bb2b2924f4f87"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="R9efc7739181e4f24"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="R09ae11d467844607"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="Ra6f327f4b4934850"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="Rce2592bc72754f45"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="R9796551a879048e9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="Rcf6d074c4c044f84"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="R9875e1671a8f485e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="Rb241442db7584f05"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="Rb9554c36e00c481f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="Rb27db3cf08924551"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="R4d8429cfff314691"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="R94a89dd8c4d049d3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="R648e22d4fe5343eb"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="R78f182d9ab1f4e7e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="Rf28b8cfb93f843d2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="R1d03c5b946dc42f8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="Re5d1d7009e80477e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="R1b3fc0723dc7423b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="Rd47ae145b0134a6d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="Ra5f593920d344ae9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="Rccfcac3a49b447a0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="Rff0d8c8ebc4446f2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="R9fa33f0ace3742aa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="R3999166ba8ee4a8a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="R0f5879bc76044ac6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="R779c5382c92f4352"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="R53b1ead233164903"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="R50dc599228004e0d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="R73f438d5c35347e3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="R67160666f3234c17"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="R86a6b1f9857b4b27"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="Ra7b1404f68d148ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="Ra1b86483cb0341fc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="R10f7b016dc8d468c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="Ra0f065dc82d64f7b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="Raaae1e904bcd430f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="R0b62b23d23dc4dc4"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="Ra469b9e34dbc4c1e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="R3091b531310d4264"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="R79e039ef16364174"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="R12fe425d4c6b4a94"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="R3fb8fbe6deb94be6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="R24473a6719924232"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="R5cda332432b84623"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="R2573a138f0814698"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="R173d8f0f935c435b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="R2b9ddc05d6054f40"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="R2d855840e4e943b0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="R3144b2039b464710"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="Rab54b8fdf2f94672"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="Rad45788eaadf4db6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="R773e673e4177445a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="R2a59bcba923243e7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="R1e5e69d76926425f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="R2ef1323aa18c4e71"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="Rc1cb802ae187498e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="R6020297d5b944b46"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="Rf7cef8e2553545f1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="R2fc578c9af344fd1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="R2285d332c2a34f71"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="R2adb8dbfa9b04aec"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="R8ce3d5d4f6e84f39"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="R195e0ac47d3d4765"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="R71963e631ead434b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="Rd898098e12d945f1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="R291ea743e7af4184"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="R3b82702cab464a4d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="R162cf5fd8a064d1c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="Rd328f5060d464008"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="R139c131c5ea640b7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="R908e777df44b4ac9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="R76ae227831df475f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="R3a2a3605ecda4f96"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="Rff9196e9c09e473f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="Rfb57cce1baed44d0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="R494717313b9e44ef"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="Rca1cf0c2dd6744ae"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="R17db40633fcc4554"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="R478484e1db6c4607"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="R400b8610053e451f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="Rda70e5a78c314e68"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="R1a54a42c3c364919"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="R60d65e6676d74f50"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="R459528deb4e24199"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="R927fbfc5eb154226"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="R9af0643888ff4be2"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="Raa45e6f9695540bc"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="R03452bb7f9e04710"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="Rcf6d18782621461f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="Rdc8783bec90b4b49"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="R4883ee43cbfe4a2e"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="Re0a28cfe88af4057"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="R20e6bc101ff342ba"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="R31f622a51d0445d8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="R699e5a2c85ae4bdf"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="R446b6fad1bc44172"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="Rb9678fc6613b4802"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="Ra69f869cd1d647b5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="R9d84a89245b445e1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="Rd27eba2ccdd7475b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="Rffa2361ad61849ad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="R1c190555e2ff40dd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="R660c9a50337d4fca"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="Rc6c08f6849ec41ab"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="R1fe4a6219d6a4863"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="R371c5a0b5fbb4edd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M6" r:id="R04c39fca96a540c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="Rc4fe086185734be0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M7" r:id="R0fa31e6ebc294c83"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="R860bccff1830444b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M8" r:id="Rceff39c193ef4ca0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="R9c2ba532ec444a8d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M9" r:id="Raac766a0b1c94fa3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="R0479e0de78d943cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M10" r:id="Ra6f3e9d66137401c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="R86455feb73464ee7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M11" r:id="Rf1e7bb2659ab48de"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="Rce31ed9c6c25412d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M12" r:id="Rcf8571e868c044b7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="R2f851b7410274570"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M13" r:id="Rb4537be10cd74edf"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M14" r:id="R95669f3db0a04f06"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M15" r:id="Rdb5b80a4dc8f4a29"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M16" r:id="Ref29e259faa3411c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="Rc9a18754eeba4d6a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M17" r:id="R144dcb081df54526"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="Rf88f2ba69319432f"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M18" r:id="R842b4e60026146fd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="R18f61253365f47b3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M19" r:id="Re941b187706049c2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="Rcb541af8b9024977"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M20" r:id="R7d284424b7fb40a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="R93f36c6ff7114604"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M21" r:id="Rb889ec0766274e88"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="Rb6b451ac69ea4a26"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M22" r:id="R3b04b62856c44504"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="R9967e3c54256410b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M23" r:id="R3b8ac412b3e74036"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="R1970ca8f78d94152"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M24" r:id="Rbce9f0b57e0e49e9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="Rcc585f28c26b44c1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M25" r:id="R6582ef87c6734035"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="R33a8bc81b7eb4ef8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M26" r:id="Rdc887ced902e4a41"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="R1d8147d6b77a4261"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M27" r:id="R89bb1b7b1f5e4d50"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="R1de29f48bde345b2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M28" r:id="Rac33425029bd4f99"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="R2d07e997c7944f1e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M29" r:id="R9cf65e6924e549e1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="R44ca41ea101f491c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M30" r:id="R60657c91a94e45eb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M31" r:id="R1d6515bb64764d11"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="R19a8ee8001094f68"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M32" r:id="R3ecd527c440d4f9e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="R6c834472efed438d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M33" r:id="R7a723dbdd59f4e34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="R732be1af650a4370"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M34" r:id="Rc81c59ec5d044567"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M35" r:id="Ra63cf19cf72d425d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="R2e0463b2ab7646da"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M36" r:id="R0c260c7e53944e30"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="R8fadd43462694e83"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M37" r:id="R3cd12ac748cc403c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="R76e9d7e71ca74d21"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M38" r:id="R30fdc7dab2254f6d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="R62f2c4d5dc1c4cda"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M39" r:id="Rc6b0a144629f47c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="Rde49077a1fcd49b4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M40" r:id="Rc35bf5b45c2b44cd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="Rebe47f783bb34691"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M41" r:id="Rf3b8183cac5342fd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="Rf0ae7c18a0c44287"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M42" r:id="R448ed97930bc40dd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="R1c6e981f88394c91"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M43" r:id="R3641cc646bda406d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="R55bf51476a4e4d52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M44" r:id="R8a639d6d8eee41fd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="Rdda65571daf044dd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M45" r:id="R658ee814aa144e2b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="Ref35ad2cb76040a8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M46" r:id="Rbd42dd82d9da4af4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="R2258693dbea8440b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M47" r:id="R4a2c6621eac34b69"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="Ra4dbf28f6b06429e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M48" r:id="R1754db0a2a1d4045"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="Rb5e864f92c1f4c25"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M49" r:id="R0e021c78914746c8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="R6c3c4fb89ae24176"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="Rde2bc38703494561"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="R3497a60799764277"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M51" r:id="R394109c134d94bb9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="R2f3f95e4b14d48ba"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M52" r:id="Rf91db18ff9c54374"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M53" r:id="R150b794c89a144e1"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="R04af90114bb34e21"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M54" r:id="R9f6853d8711040dc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="R4623286bae1a4a5e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M55" r:id="Rf46084cfa1e44454"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="Rb0cdf6fe5dda4b6d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M56" r:id="R7f55d37bfbae4c34"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="Re4b5dbcda87b45f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M57" r:id="Rc6feab8cb6e0494a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="R47341014db14476b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M58" r:id="Rccb2840d99074fe9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="R95e1a969724e4759"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M59" r:id="R05ec3815d5e64312"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="Rbbeec2b5fdd443d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M60" r:id="R68baba156a344106"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="R7317bcfd1255405b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M61" r:id="R4ebfd7799f5144f4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="Rff77ba8debbc4370"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M62" r:id="R1647d485733f4589"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M63" r:id="Re708299641444d52"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="Re1a43e8e2d614e62"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M64" r:id="R03f94de11d02494b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="Ra16e39f87daa4eb4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M65" r:id="R08711d52da6d4007"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="R8ee7c32dfd2e44d6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M66" r:id="Rd9f0144dce9849f3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="Rb84d03a882e8485a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M67" r:id="R287fa53b95ab4553"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="R12ec92d337914285"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M68" r:id="R6e7a66dfe4ac4c80"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="R55091569e05c4652"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M69" r:id="R8070c662a04d48f8"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="Rf88d5fcd70ea474a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M70" r:id="R86e8796393ac4190"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="R42acd4a1374e42a0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M71" r:id="Rc4fee27ee2b547fa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="Rdf67c997655d4afc"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M72" r:id="R61f26fc3c8334d42"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="R233a84f3caac4dbd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M73" r:id="Rd5b2caf47aa54ec5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="Rfee41d2335c042d3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M74" r:id="R8eff4904c743413e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="R29949fb9d8994284"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M75" r:id="Ra6986efd42154a5e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="R333f3fbd9b124578"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa6daa0670c94307"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc026461fe183490b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8421,53 +8427,53 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="Rb2e9dced2100409d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="Rc99d067a436143e0"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="R9bffbe35e61b4d1f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="Re94df286ce1b4309"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="R68e3a2ff7abe498d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="Rdb1297f5e7f94837"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="R6805a6d25c9d448d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="Rd05da4ed69b949c7"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="R3916bb8f427e46e6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="Rd96348b7dcf14726"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="R222801da15b44d08"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="Rf11f75e093e44c0f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="Rc285aa1769e84d23"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="R0a2482aa24484d6b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="Re0a1e83422164b7f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="Rb6ac78c132f94528"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="Raf60fd2be469491c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="R86f6011f3471409a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="Rc045dfa479b74794"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="R273d220cd7614b9b"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="R12480cd09a4c42fd"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="Refddc30035c547b1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="R14446c5d427c4dc3"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="R99877480c0e546be"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="Rcf2735c8e377407d"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="R5798414daf0f4a57"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="Ra03746c70fb54b06"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="R2fdc1138fbd24a50"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="R3dad4d17eac949db"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="R8bea400fffd44925"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="R35cc60f8b16445db"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="R41d6ab6c20bc4e2f"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="Rb71024a5f91f49f9"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="Rc1cd6d48fc154bd5"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="R8049bbf49e304270"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="Rc0b6d99890a344ad"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="R9cacb0d355f2444c"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="R8bbc62e4d5ec4f28"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="Rd0b097924f904ba1"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="R538a7c9c3c0040fa"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="R4e7554a4500a4768"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="Rfc11e0c7c2aa4c55"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="Re217cefebf26408a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="R8ada0bb51bb94a3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="R73b7e98c7a014864"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="R85fdeeb4811a4bca"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="Rfa1cbcd7cd5f4771"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="R0dff558fd6784fd9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="Rbc9a13a37c684fe3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="R921b458400254057"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="Rb791312451d94bdb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="R24cbd3e2ca5f49a3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="Rd5bdeb08bdbd4ce2"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="R694c31a9a17645d4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="R1586bb9e5b2b4c1a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="Rf71b6107c88040d5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="Rc5b6befb0e8d4904"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="Rcff2a0b355c44520"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="Rf869c6ca07824390"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="Rdf928d9c40d64a99"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="Rbe1fd28de2e34c60"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="Rf767f53067ed4737"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="R05dc6510bf7e49eb"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="Rd4ceb35855fe43b3"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="Rd94fd0aab86543bd"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="R0894279333764c51"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="R7fd014721dd5471c"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="Rffe49336b48a49ac"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="R1424c63b01c1424b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="R108a1ef7bab942b5"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="Ra181b241bd394eec"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="Rcaec8a016e894b3e"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="R01d2dffcf3b44bf4"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="R585be56971024981"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="R6ac2aa6ca17c4406"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="R816d64bfcd6c4944"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="Rf6982bfcbbe346e9"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="R3a476c5edffc43fa"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="R0b1ee29c6ceb4b94"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C42" r:id="R17dece7c430a498a"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C43" r:id="Rd0ccd11360264c37"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C44" r:id="R86faacacc3404cd0"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C45" r:id="R67776afbea58427b"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C46" r:id="R39cf34e9fde24740"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C47" r:id="R8720b884996a41ad"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C48" r:id="Rd026cf27305c4777"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R149fa86851e74097"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f1b305c8834a54"/>
   </x:tableParts>
 </x:worksheet>
 </file>